--- a/assets/data/excel/achievement.xlsx
+++ b/assets/data/excel/achievement.xlsx
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>累计获得10000赛博币</t>
+          <t>累计获得10000菌丝</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>累计获得1000000赛博币</t>
+          <t>累计获得1000000菌丝</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>累计获得10000赛博币</t>
+          <t>累计获得10000菌丝</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>累计获得100000000赛博币</t>
+          <t>累计获得100000000菌丝</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>累计获得1000000赛博币</t>
+          <t>累计获得1000000菌丝</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>累计获得100000000赛博币</t>
+          <t>累计获得100000000菌丝</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">

--- a/assets/data/excel/achievement.xlsx
+++ b/assets/data/excel/achievement.xlsx
@@ -583,7 +583,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>180</v>
+        <v>1440</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>120</v>
+        <v>840</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>350</v>
+        <v>3500</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>

--- a/assets/data/excel/achievement.xlsx
+++ b/assets/data/excel/achievement.xlsx
@@ -654,8 +654,6 @@
           <t>[{"type":"mycelium","amount":500}]</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="b">
         <v>0</v>
       </c>
@@ -702,7 +700,6 @@
           <t>TITLE_EXP_002</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="b">
         <v>0</v>
       </c>
@@ -749,7 +746,6 @@
           <t>TITLE_EXP_003</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="b">
         <v>0</v>
       </c>
@@ -796,7 +792,6 @@
           <t>TITLE_EXP_004</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="b">
         <v>0</v>
       </c>
@@ -843,7 +838,6 @@
           <t>TITLE_EXP_005</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="b">
         <v>0</v>
       </c>
@@ -890,7 +884,6 @@
           <t>TITLE_EXP_006</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="b">
         <v>0</v>
       </c>
@@ -937,7 +930,6 @@
           <t>TITLE_EXP_007</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="b">
         <v>0</v>
       </c>
@@ -984,7 +976,6 @@
           <t>TITLE_EXP_008</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="b">
         <v>0</v>
       </c>
@@ -1031,7 +1022,6 @@
           <t>TITLE_EXP_009</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="b">
         <v>0</v>
       </c>
@@ -1078,7 +1068,6 @@
           <t>TITLE_EXP_010</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1114,6 @@
           <t>TITLE_EXP_011</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="b">
         <v>0</v>
       </c>
@@ -1218,8 +1206,6 @@
           <t>[{"type":"mycelium","amount":1000}]</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="b">
         <v>0</v>
       </c>
@@ -1317,7 +1303,6 @@
           <t>TITLE_EXP_015_LE</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="b">
         <v>0</v>
       </c>
@@ -1359,8 +1344,6 @@
           <t>[{"type":"mycelium","amount":300}]</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="b">
         <v>0</v>
       </c>
@@ -1407,7 +1390,6 @@
           <t>TITLE_CMB_002</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="b">
         <v>0</v>
       </c>
@@ -1500,8 +1482,6 @@
           <t>[{"type":"mycelium","amount":500}]</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1528,6 @@
           <t>TITLE_CMB_005</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="b">
         <v>0</v>
       </c>
@@ -1590,8 +1569,6 @@
           <t>[{"type":"sourceCore","amount":200}]</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="b">
         <v>0</v>
       </c>
@@ -1633,8 +1610,6 @@
           <t>[{"type":"sourceCore","amount":300}]</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="b">
         <v>0</v>
       </c>
@@ -1727,8 +1702,6 @@
           <t>[{"type":"mycelium","amount":1000}]</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1748,6 @@
           <t>TITLE_CMB_010</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="b">
         <v>0</v>
       </c>
@@ -1817,8 +1789,6 @@
           <t>[{"type":"mycelium","amount":500}]</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="b">
         <v>0</v>
       </c>
@@ -1860,8 +1830,6 @@
           <t>[{"type":"sourceCore","amount":300}]</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="b">
         <v>0</v>
       </c>
@@ -1908,7 +1876,6 @@
           <t>TITLE_COL_003</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="b">
         <v>0</v>
       </c>
@@ -2001,8 +1968,6 @@
           <t>[{"type":"sourceCore","amount":200}]</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="b">
         <v>0</v>
       </c>
@@ -2049,7 +2014,6 @@
           <t>TITLE_COL_006</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="b">
         <v>0</v>
       </c>
@@ -2096,7 +2060,6 @@
           <t>TITLE_COL_007</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="b">
         <v>0</v>
       </c>
@@ -2130,16 +2093,16 @@
           <t>own_all_quality</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>[{"type":"sourceCore","amount":1000}]</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="b">
         <v>0</v>
       </c>
@@ -2173,15 +2136,16 @@
           <t>own_all_quality</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>[{"type":"sourceCore","amount":2000},{"type":"portrait_frame","id":"FRAME_COL_009"}]</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>FRAME_COL_009</t>
@@ -2220,15 +2184,16 @@
           <t>own_all_quality</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>[{"type":"sourceCore","amount":3000},{"type":"portrait_frame","id":"FRAME_COL_010"}]</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>FRAME_COL_010</t>
@@ -2275,8 +2240,6 @@
           <t>[{"type":"mycelium","amount":300}]</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="b">
         <v>0</v>
       </c>
@@ -2318,8 +2281,6 @@
           <t>[{"type":"sourceCore","amount":200}]</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="b">
         <v>0</v>
       </c>
@@ -2366,7 +2327,6 @@
           <t>TITLE_GRW_003</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="b">
         <v>0</v>
       </c>
@@ -2459,8 +2419,6 @@
           <t>[{"type":"mycelium","amount":500}]</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="b">
         <v>0</v>
       </c>
@@ -2502,8 +2460,6 @@
           <t>[{"type":"sourceCore","amount":300}]</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="b">
         <v>0</v>
       </c>
@@ -2545,7 +2501,6 @@
           <t>[{"type":"sourceCore","amount":500},{"type":"portrait_frame","id":"FRAME_GRW_007"}]</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>FRAME_GRW_007</t>
@@ -2592,8 +2547,6 @@
           <t>[{"type":"mycelium","amount":500}]</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="b">
         <v>0</v>
       </c>
@@ -2640,7 +2593,6 @@
           <t>TITLE_GRW_009_LE</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="b">
         <v>0</v>
       </c>
@@ -2682,8 +2634,6 @@
           <t>[{"type":"mycelium","amount":300}]</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="b">
         <v>0</v>
       </c>
@@ -2730,7 +2680,6 @@
           <t>TITLE_SOC_001</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2726,6 @@
           <t>TITLE_SOC_002</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="b">
         <v>0</v>
       </c>
@@ -2977,7 +2925,6 @@
           <t>TITLE_SPC_001</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="b">
         <v>1</v>
       </c>
@@ -3024,7 +2971,6 @@
           <t>TITLE_SPC_002</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="b">
         <v>1</v>
       </c>
